--- a/backend/import_files/device-import-T_7BA4E9A8DA6B.xlsx
+++ b/backend/import_files/device-import-T_7BA4E9A8DA6B.xlsx
@@ -573,7 +573,7 @@
     <col min="16" max="16" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -623,7 +623,7 @@
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20.25">
       <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
@@ -669,7 +669,7 @@
       </c>
       <c r="P2" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.25">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -715,7 +715,7 @@
       </c>
       <c r="P3" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="20.25">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -759,7 +759,7 @@
       </c>
       <c r="P4" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20.25">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -803,7 +803,7 @@
       </c>
       <c r="P5" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="20.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
